--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135958228</v>
+        <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>91564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,34 +2155,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>4189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Ytternäs, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702766</v>
+        <v>702803</v>
       </c>
       <c r="R15" t="n">
-        <v>6650506</v>
+        <v>6650289</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,92 +2235,66 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958228</t>
+          <t>https://artportalen.se/Sighting/137373612</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80855842</v>
+        <v>135958228</v>
       </c>
       <c r="B16" t="n">
-        <v>93189</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702812</v>
+        <v>702766</v>
       </c>
       <c r="R16" t="n">
-        <v>6650287</v>
+        <v>6650506</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2347,12 +2321,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,34 +2345,48 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855842</t>
+          <t>https://artportalen.se/Sighting/135958228</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80855853</v>
+        <v>80855842</v>
       </c>
       <c r="B17" t="n">
-        <v>93215</v>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,25 +2394,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2423,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702786</v>
+        <v>702812</v>
       </c>
       <c r="R17" t="n">
-        <v>6650299</v>
+        <v>6650287</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2485,38 +2491,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855853</t>
+          <t>https://artportalen.se/Sighting/80855842</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80855909</v>
+        <v>80855853</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>93215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2535,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702670</v>
+        <v>702786</v>
       </c>
       <c r="R18" t="n">
-        <v>6650312</v>
+        <v>6650299</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2591,50 +2597,42 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855909</t>
+          <t>https://artportalen.se/Sighting/80855853</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80855888</v>
+        <v>80855909</v>
       </c>
       <c r="B19" t="n">
-        <v>93233</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2643,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702710</v>
+        <v>702670</v>
       </c>
       <c r="R19" t="n">
-        <v>6650433</v>
+        <v>6650312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2705,13 +2703,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855888</t>
+          <t>https://artportalen.se/Sighting/80855909</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80855902</v>
+        <v>80855888</v>
       </c>
       <c r="B20" t="n">
         <v>93233</v>
@@ -2739,8 +2737,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2749,10 +2755,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702914</v>
+        <v>702710</v>
       </c>
       <c r="R20" t="n">
-        <v>6650573</v>
+        <v>6650433</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2811,56 +2817,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855902</t>
+          <t>https://artportalen.se/Sighting/80855888</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135958207</v>
+        <v>80855902</v>
       </c>
       <c r="B21" t="n">
-        <v>58003</v>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702684</v>
+        <v>702914</v>
       </c>
       <c r="R21" t="n">
-        <v>6650305</v>
+        <v>6650573</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2887,22 +2891,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2911,73 +2905,69 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958207</t>
+          <t>https://artportalen.se/Sighting/80855902</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135958229</v>
+        <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>58003</v>
+        <v>93497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Ytternäs, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702754</v>
+        <v>702828</v>
       </c>
       <c r="R22" t="n">
-        <v>6650509</v>
+        <v>6650108</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3004,22 +2994,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,67 +3024,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958229</t>
+          <t>https://artportalen.se/Sighting/137373610</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135958250</v>
+        <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>58003</v>
+        <v>93445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Ytternäs, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702870</v>
+        <v>702845</v>
       </c>
       <c r="R23" t="n">
-        <v>6650207</v>
+        <v>6650061</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,22 +3109,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Under sten i blockrik tallskog med sandig morän</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,33 +3138,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958250</t>
+          <t>https://artportalen.se/Sighting/137373611</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135958196</v>
+        <v>135958207</v>
       </c>
       <c r="B24" t="n">
-        <v>4783</v>
+        <v>58003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3179,34 +3173,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702744</v>
+        <v>702684</v>
       </c>
       <c r="R24" t="n">
-        <v>6650269</v>
+        <v>6650305</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3238,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3247,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,26 +3258,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3294,16 +3273,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958196</t>
+          <t>https://artportalen.se/Sighting/135958207</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135958210</v>
+        <v>135958229</v>
       </c>
       <c r="B25" t="n">
-        <v>4783</v>
+        <v>58003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,34 +3290,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702696</v>
+        <v>702754</v>
       </c>
       <c r="R25" t="n">
-        <v>6650341</v>
+        <v>6650509</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3370,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,26 +3375,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3426,16 +3390,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958210</t>
+          <t>https://artportalen.se/Sighting/135958229</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135958248</v>
+        <v>135958250</v>
       </c>
       <c r="B26" t="n">
-        <v>4783</v>
+        <v>58003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,34 +3407,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702886</v>
+        <v>702870</v>
       </c>
       <c r="R26" t="n">
-        <v>6650190</v>
+        <v>6650207</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3502,7 +3471,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3481,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,26 +3492,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3558,56 +3507,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958248</t>
+          <t>https://artportalen.se/Sighting/135958250</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135958211</v>
+        <v>135958196</v>
       </c>
       <c r="B27" t="n">
-        <v>58167</v>
+        <v>4783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702716</v>
+        <v>702744</v>
       </c>
       <c r="R27" t="n">
-        <v>6650349</v>
+        <v>6650269</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3639,7 +3583,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3593,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3660,6 +3604,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3675,60 +3639,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958211</t>
+          <t>https://artportalen.se/Sighting/135958196</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135958216</v>
+        <v>135958210</v>
       </c>
       <c r="B28" t="n">
-        <v>58167</v>
+        <v>4783</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702829</v>
+        <v>702696</v>
       </c>
       <c r="R28" t="n">
-        <v>6650555</v>
+        <v>6650341</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3760,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3781,6 +3736,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3796,56 +3771,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958216</t>
+          <t>https://artportalen.se/Sighting/135958210</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135958226</v>
+        <v>135958248</v>
       </c>
       <c r="B29" t="n">
-        <v>58167</v>
+        <v>4783</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702794</v>
+        <v>702886</v>
       </c>
       <c r="R29" t="n">
-        <v>6650513</v>
+        <v>6650190</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3877,7 +3847,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3887,7 +3857,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,6 +3868,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3913,13 +3903,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958226</t>
+          <t>https://artportalen.se/Sighting/135958248</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135958246</v>
+        <v>135958211</v>
       </c>
       <c r="B30" t="n">
         <v>58167</v>
@@ -3947,11 +3937,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -3963,10 +3949,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702901</v>
+        <v>702716</v>
       </c>
       <c r="R30" t="n">
-        <v>6650251</v>
+        <v>6650349</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3998,7 +3984,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4008,7 +3994,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,44 +4020,48 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958246</t>
+          <t>https://artportalen.se/Sighting/135958211</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135958227</v>
+        <v>135958216</v>
       </c>
       <c r="B31" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4080,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702772</v>
+        <v>702829</v>
       </c>
       <c r="R31" t="n">
-        <v>6650499</v>
+        <v>6650555</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4115,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4125,7 +4115,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,51 +4141,56 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958227</t>
+          <t>https://artportalen.se/Sighting/135958216</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135958241</v>
+        <v>135958226</v>
       </c>
       <c r="B32" t="n">
-        <v>5202</v>
+        <v>58167</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702806</v>
+        <v>702794</v>
       </c>
       <c r="R32" t="n">
-        <v>6650362</v>
+        <v>6650513</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4227,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4237,7 +4232,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,48 +4258,48 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958241</t>
+          <t>https://artportalen.se/Sighting/135958226</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135958231</v>
+        <v>135958246</v>
       </c>
       <c r="B33" t="n">
-        <v>99342</v>
+        <v>58167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4313,10 +4308,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702736</v>
+        <v>702901</v>
       </c>
       <c r="R33" t="n">
-        <v>6650508</v>
+        <v>6650251</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4348,7 +4343,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4358,7 +4353,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4384,48 +4379,44 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958231</t>
+          <t>https://artportalen.se/Sighting/135958246</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135958232</v>
+        <v>135958227</v>
       </c>
       <c r="B34" t="n">
-        <v>99342</v>
+        <v>58162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4434,10 +4425,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702734</v>
+        <v>702772</v>
       </c>
       <c r="R34" t="n">
-        <v>6650509</v>
+        <v>6650499</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4469,7 +4460,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4479,7 +4470,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4505,16 +4496,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958232</t>
+          <t>https://artportalen.se/Sighting/135958227</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>80855845</v>
+        <v>135958241</v>
       </c>
       <c r="B35" t="n">
-        <v>106244</v>
+        <v>5202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4522,38 +4513,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702804</v>
+        <v>702806</v>
       </c>
       <c r="R35" t="n">
-        <v>6650298</v>
+        <v>6650362</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4580,12 +4567,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4594,73 +4591,77 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855845</t>
+          <t>https://artportalen.se/Sighting/135958241</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80855858</v>
+        <v>135958231</v>
       </c>
       <c r="B36" t="n">
-        <v>106244</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702821</v>
+        <v>702736</v>
       </c>
       <c r="R36" t="n">
-        <v>6650318</v>
+        <v>6650508</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4687,12 +4688,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4701,73 +4712,77 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855858</t>
+          <t>https://artportalen.se/Sighting/135958231</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>80855895</v>
+        <v>135958232</v>
       </c>
       <c r="B37" t="n">
-        <v>106244</v>
+        <v>99342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702841</v>
+        <v>702734</v>
       </c>
       <c r="R37" t="n">
-        <v>6650555</v>
+        <v>6650509</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4794,12 +4809,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,34 +4833,33 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855895</t>
+          <t>https://artportalen.se/Sighting/135958232</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135958214</v>
+        <v>80855845</v>
       </c>
       <c r="B38" t="n">
-        <v>106483</v>
+        <v>106244</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4861,16 +4885,20 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702732</v>
+        <v>702804</v>
       </c>
       <c r="R38" t="n">
-        <v>6650512</v>
+        <v>6650298</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4897,22 +4925,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4921,33 +4939,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958214</t>
+          <t>https://artportalen.se/Sighting/80855845</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135958234</v>
+        <v>80855858</v>
       </c>
       <c r="B39" t="n">
-        <v>106483</v>
+        <v>106244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4973,16 +4992,20 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702750</v>
+        <v>702821</v>
       </c>
       <c r="R39" t="n">
-        <v>6650455</v>
+        <v>6650318</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5009,22 +5032,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5033,33 +5046,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958234</t>
+          <t>https://artportalen.se/Sighting/80855858</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135958242</v>
+        <v>80855895</v>
       </c>
       <c r="B40" t="n">
-        <v>106483</v>
+        <v>106244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5085,16 +5099,20 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>702803</v>
+        <v>702841</v>
       </c>
       <c r="R40" t="n">
-        <v>6650332</v>
+        <v>6650555</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5121,22 +5139,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5145,33 +5153,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958242</t>
+          <t>https://artportalen.se/Sighting/80855895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>80855871</v>
+        <v>135958214</v>
       </c>
       <c r="B41" t="n">
-        <v>101326</v>
+        <v>106483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5179,38 +5188,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>702790</v>
+        <v>702732</v>
       </c>
       <c r="R41" t="n">
-        <v>6650382</v>
+        <v>6650512</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5237,12 +5242,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5251,34 +5266,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855871</t>
+          <t>https://artportalen.se/Sighting/135958214</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135958198</v>
+        <v>135958234</v>
       </c>
       <c r="B42" t="n">
-        <v>101552</v>
+        <v>106483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5286,21 +5300,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5310,10 +5324,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>702738</v>
+        <v>702750</v>
       </c>
       <c r="R42" t="n">
-        <v>6650315</v>
+        <v>6650455</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5345,7 +5359,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5369,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5381,16 +5395,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958198</t>
+          <t>https://artportalen.se/Sighting/135958234</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135958201</v>
+        <v>135958242</v>
       </c>
       <c r="B43" t="n">
-        <v>101552</v>
+        <v>106483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,21 +5412,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5422,10 +5436,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>702732</v>
+        <v>702803</v>
       </c>
       <c r="R43" t="n">
-        <v>6650309</v>
+        <v>6650332</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5457,7 +5471,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5467,7 +5481,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5493,16 +5507,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958201</t>
+          <t>https://artportalen.se/Sighting/135958242</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135958218</v>
+        <v>80855871</v>
       </c>
       <c r="B44" t="n">
-        <v>101552</v>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5528,16 +5542,20 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>702844</v>
+        <v>702790</v>
       </c>
       <c r="R44" t="n">
-        <v>6650565</v>
+        <v>6650382</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5564,22 +5582,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5588,30 +5596,31 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958218</t>
+          <t>https://artportalen.se/Sighting/80855871</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135958224</v>
+        <v>135958198</v>
       </c>
       <c r="B45" t="n">
         <v>101552</v>
@@ -5646,10 +5655,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>702836</v>
+        <v>702738</v>
       </c>
       <c r="R45" t="n">
-        <v>6650546</v>
+        <v>6650315</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5681,7 +5690,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5691,7 +5700,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5717,13 +5726,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958224</t>
+          <t>https://artportalen.se/Sighting/135958198</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135958225</v>
+        <v>135958201</v>
       </c>
       <c r="B46" t="n">
         <v>101552</v>
@@ -5758,10 +5767,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>702833</v>
+        <v>702732</v>
       </c>
       <c r="R46" t="n">
-        <v>6650537</v>
+        <v>6650309</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5793,7 +5802,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5803,7 +5812,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5829,13 +5838,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958225</t>
+          <t>https://artportalen.se/Sighting/135958201</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135958235</v>
+        <v>135958218</v>
       </c>
       <c r="B47" t="n">
         <v>101552</v>
@@ -5870,10 +5879,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>702742</v>
+        <v>702844</v>
       </c>
       <c r="R47" t="n">
-        <v>6650450</v>
+        <v>6650565</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5905,7 +5914,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5915,7 +5924,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5941,13 +5950,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958235</t>
+          <t>https://artportalen.se/Sighting/135958218</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135958238</v>
+        <v>135958224</v>
       </c>
       <c r="B48" t="n">
         <v>101552</v>
@@ -5982,10 +5991,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>702791</v>
+        <v>702836</v>
       </c>
       <c r="R48" t="n">
-        <v>6650389</v>
+        <v>6650546</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6017,7 +6026,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6027,7 +6036,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6052,6 +6061,342 @@
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958224</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135958225</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>702833</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6650537</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958225</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135958235</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>702742</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6650450</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958235</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135958238</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6650389</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135958238</t>
         </is>
@@ -6106,6 +6451,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,38 +3162,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135958207</v>
+        <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>58003</v>
+        <v>93447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6055</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3202,13 +3206,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702684</v>
+        <v>702832</v>
       </c>
       <c r="R24" t="n">
-        <v>6650305</v>
+        <v>6650047</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,22 +3236,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Återbesök av känt fynd upptäckt av Cajsa Björkén. Under stenblock.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,24 +3271,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Johan Lindell, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958207</t>
+          <t>https://artportalen.se/Sighting/137387706</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135958229</v>
+        <v>135958207</v>
       </c>
       <c r="B25" t="n">
         <v>58003</v>
@@ -3310,7 +3319,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3319,10 +3328,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702754</v>
+        <v>702684</v>
       </c>
       <c r="R25" t="n">
-        <v>6650509</v>
+        <v>6650305</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3354,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3390,13 +3399,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958229</t>
+          <t>https://artportalen.se/Sighting/135958207</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135958250</v>
+        <v>135958229</v>
       </c>
       <c r="B26" t="n">
         <v>58003</v>
@@ -3436,10 +3445,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702870</v>
+        <v>702754</v>
       </c>
       <c r="R26" t="n">
-        <v>6650207</v>
+        <v>6650509</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3471,7 +3480,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3490,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,16 +3516,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958250</t>
+          <t>https://artportalen.se/Sighting/135958229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135958196</v>
+        <v>135958250</v>
       </c>
       <c r="B27" t="n">
-        <v>4783</v>
+        <v>58003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,34 +3533,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702744</v>
+        <v>702870</v>
       </c>
       <c r="R27" t="n">
-        <v>6650269</v>
+        <v>6650207</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3583,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,26 +3618,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3639,13 +3633,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958196</t>
+          <t>https://artportalen.se/Sighting/135958250</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135958210</v>
+        <v>135958196</v>
       </c>
       <c r="B28" t="n">
         <v>4783</v>
@@ -3680,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702696</v>
+        <v>702744</v>
       </c>
       <c r="R28" t="n">
-        <v>6650341</v>
+        <v>6650269</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3715,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,13 +3765,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958210</t>
+          <t>https://artportalen.se/Sighting/135958196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135958248</v>
+        <v>135958210</v>
       </c>
       <c r="B29" t="n">
         <v>4783</v>
@@ -3812,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702886</v>
+        <v>702696</v>
       </c>
       <c r="R29" t="n">
-        <v>6650190</v>
+        <v>6650341</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3847,7 +3841,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3857,7 +3851,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,56 +3897,51 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958248</t>
+          <t>https://artportalen.se/Sighting/135958210</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135958211</v>
+        <v>135958248</v>
       </c>
       <c r="B30" t="n">
-        <v>58167</v>
+        <v>4783</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702716</v>
+        <v>702886</v>
       </c>
       <c r="R30" t="n">
-        <v>6650349</v>
+        <v>6650190</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3984,7 +3973,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3994,7 +3983,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,6 +3994,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4020,13 +4029,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958211</t>
+          <t>https://artportalen.se/Sighting/135958248</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135958216</v>
+        <v>135958211</v>
       </c>
       <c r="B31" t="n">
         <v>58167</v>
@@ -4054,11 +4063,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -4070,10 +4075,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702829</v>
+        <v>702716</v>
       </c>
       <c r="R31" t="n">
-        <v>6650555</v>
+        <v>6650349</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4110,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4120,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,13 +4146,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958216</t>
+          <t>https://artportalen.se/Sighting/135958211</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135958226</v>
+        <v>135958216</v>
       </c>
       <c r="B32" t="n">
         <v>58167</v>
@@ -4175,7 +4180,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702794</v>
+        <v>702829</v>
       </c>
       <c r="R32" t="n">
-        <v>6650513</v>
+        <v>6650555</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4222,7 +4231,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,7 +4241,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4258,13 +4267,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958226</t>
+          <t>https://artportalen.se/Sighting/135958216</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135958246</v>
+        <v>135958226</v>
       </c>
       <c r="B33" t="n">
         <v>58167</v>
@@ -4292,11 +4301,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -4308,10 +4313,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702901</v>
+        <v>702794</v>
       </c>
       <c r="R33" t="n">
-        <v>6650251</v>
+        <v>6650513</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4343,7 +4348,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4353,7 +4358,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,44 +4384,48 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958246</t>
+          <t>https://artportalen.se/Sighting/135958226</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135958227</v>
+        <v>135958246</v>
       </c>
       <c r="B34" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4425,10 +4434,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702772</v>
+        <v>702901</v>
       </c>
       <c r="R34" t="n">
-        <v>6650499</v>
+        <v>6650251</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4460,7 +4469,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4470,7 +4479,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4496,16 +4505,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958227</t>
+          <t>https://artportalen.se/Sighting/135958246</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135958241</v>
+        <v>135958227</v>
       </c>
       <c r="B35" t="n">
-        <v>5202</v>
+        <v>58162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,16 +4522,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4531,16 +4540,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702806</v>
+        <v>702772</v>
       </c>
       <c r="R35" t="n">
-        <v>6650362</v>
+        <v>6650499</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4572,7 +4586,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4582,7 +4596,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4608,60 +4622,51 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958241</t>
+          <t>https://artportalen.se/Sighting/135958227</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135958231</v>
+        <v>135958241</v>
       </c>
       <c r="B36" t="n">
-        <v>99342</v>
+        <v>5202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702736</v>
+        <v>702806</v>
       </c>
       <c r="R36" t="n">
-        <v>6650508</v>
+        <v>6650362</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4693,7 +4698,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4703,7 +4708,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,13 +4734,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958231</t>
+          <t>https://artportalen.se/Sighting/135958241</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135958232</v>
+        <v>135958231</v>
       </c>
       <c r="B37" t="n">
         <v>99342</v>
@@ -4765,7 +4770,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4779,10 +4784,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702734</v>
+        <v>702736</v>
       </c>
       <c r="R37" t="n">
-        <v>6650509</v>
+        <v>6650508</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4814,7 +4819,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4824,7 +4829,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4850,55 +4855,60 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958232</t>
+          <t>https://artportalen.se/Sighting/135958231</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>80855845</v>
+        <v>135958232</v>
       </c>
       <c r="B38" t="n">
-        <v>106244</v>
+        <v>99342</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702804</v>
+        <v>702734</v>
       </c>
       <c r="R38" t="n">
-        <v>6650298</v>
+        <v>6650509</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4925,12 +4935,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4939,31 +4959,30 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855845</t>
+          <t>https://artportalen.se/Sighting/135958232</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>80855858</v>
+        <v>80855845</v>
       </c>
       <c r="B39" t="n">
         <v>106244</v>
@@ -5002,10 +5021,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702821</v>
+        <v>702804</v>
       </c>
       <c r="R39" t="n">
-        <v>6650318</v>
+        <v>6650298</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5064,13 +5083,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855858</t>
+          <t>https://artportalen.se/Sighting/80855845</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>80855895</v>
+        <v>80855858</v>
       </c>
       <c r="B40" t="n">
         <v>106244</v>
@@ -5109,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>702841</v>
+        <v>702821</v>
       </c>
       <c r="R40" t="n">
-        <v>6650555</v>
+        <v>6650318</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5171,16 +5190,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855895</t>
+          <t>https://artportalen.se/Sighting/80855858</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135958214</v>
+        <v>80855895</v>
       </c>
       <c r="B41" t="n">
-        <v>106483</v>
+        <v>106244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5206,16 +5225,20 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>702732</v>
+        <v>702841</v>
       </c>
       <c r="R41" t="n">
-        <v>6650512</v>
+        <v>6650555</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5242,22 +5265,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5266,30 +5279,31 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958214</t>
+          <t>https://artportalen.se/Sighting/80855895</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135958234</v>
+        <v>135958214</v>
       </c>
       <c r="B42" t="n">
         <v>106483</v>
@@ -5324,10 +5338,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>702750</v>
+        <v>702732</v>
       </c>
       <c r="R42" t="n">
-        <v>6650455</v>
+        <v>6650512</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5359,7 +5373,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5369,7 +5383,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5395,13 +5409,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958234</t>
+          <t>https://artportalen.se/Sighting/135958214</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135958242</v>
+        <v>135958234</v>
       </c>
       <c r="B43" t="n">
         <v>106483</v>
@@ -5436,10 +5450,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>702803</v>
+        <v>702750</v>
       </c>
       <c r="R43" t="n">
-        <v>6650332</v>
+        <v>6650455</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5471,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5481,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5507,16 +5521,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958242</t>
+          <t>https://artportalen.se/Sighting/135958234</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80855871</v>
+        <v>135958242</v>
       </c>
       <c r="B44" t="n">
-        <v>101326</v>
+        <v>106483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,38 +5538,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>702790</v>
+        <v>702803</v>
       </c>
       <c r="R44" t="n">
-        <v>6650382</v>
+        <v>6650332</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5582,12 +5592,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5596,34 +5616,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855871</t>
+          <t>https://artportalen.se/Sighting/135958242</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135958198</v>
+        <v>80855871</v>
       </c>
       <c r="B45" t="n">
-        <v>101552</v>
+        <v>101326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5649,16 +5668,20 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skogshult, Upl</t>
+          <t>Skogshult, N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>702738</v>
+        <v>702790</v>
       </c>
       <c r="R45" t="n">
-        <v>6650315</v>
+        <v>6650382</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5685,22 +5708,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5709,30 +5722,31 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958198</t>
+          <t>https://artportalen.se/Sighting/80855871</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135958201</v>
+        <v>135958198</v>
       </c>
       <c r="B46" t="n">
         <v>101552</v>
@@ -5767,10 +5781,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>702732</v>
+        <v>702738</v>
       </c>
       <c r="R46" t="n">
-        <v>6650309</v>
+        <v>6650315</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5802,7 +5816,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5812,7 +5826,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5838,13 +5852,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958201</t>
+          <t>https://artportalen.se/Sighting/135958198</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135958218</v>
+        <v>135958201</v>
       </c>
       <c r="B47" t="n">
         <v>101552</v>
@@ -5879,10 +5893,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>702844</v>
+        <v>702732</v>
       </c>
       <c r="R47" t="n">
-        <v>6650565</v>
+        <v>6650309</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5914,7 +5928,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5924,7 +5938,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5950,13 +5964,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958218</t>
+          <t>https://artportalen.se/Sighting/135958201</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135958224</v>
+        <v>135958218</v>
       </c>
       <c r="B48" t="n">
         <v>101552</v>
@@ -5991,10 +6005,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>702836</v>
+        <v>702844</v>
       </c>
       <c r="R48" t="n">
-        <v>6650546</v>
+        <v>6650565</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6026,7 +6040,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6036,7 +6050,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6062,13 +6076,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958224</t>
+          <t>https://artportalen.se/Sighting/135958218</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135958225</v>
+        <v>135958224</v>
       </c>
       <c r="B49" t="n">
         <v>101552</v>
@@ -6103,10 +6117,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>702833</v>
+        <v>702836</v>
       </c>
       <c r="R49" t="n">
-        <v>6650537</v>
+        <v>6650546</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6138,7 +6152,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6148,7 +6162,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6174,13 +6188,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958225</t>
+          <t>https://artportalen.se/Sighting/135958224</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135958235</v>
+        <v>135958225</v>
       </c>
       <c r="B50" t="n">
         <v>101552</v>
@@ -6215,10 +6229,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>702742</v>
+        <v>702833</v>
       </c>
       <c r="R50" t="n">
-        <v>6650450</v>
+        <v>6650537</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6250,7 +6264,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6260,7 +6274,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6286,13 +6300,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135958235</t>
+          <t>https://artportalen.se/Sighting/135958225</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135958238</v>
+        <v>135958235</v>
       </c>
       <c r="B51" t="n">
         <v>101552</v>
@@ -6327,10 +6341,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>702791</v>
+        <v>702742</v>
       </c>
       <c r="R51" t="n">
-        <v>6650389</v>
+        <v>6650450</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6362,7 +6376,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6372,7 +6386,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6397,6 +6411,118 @@
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958235</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135958238</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6650389</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135958238</t>
         </is>
@@ -6454,6 +6580,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91566</v>
+        <v>91571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91571</v>
+        <v>91583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Lindell, Cajsa Björkén</t>
+          <t>Cajsa Björkén, Johan Lindell</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Johan Lindell</t>
+          <t>Johan Lindell, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91584</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>137373612</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137373610</v>
       </c>
       <c r="B22" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137373611</v>
       </c>
       <c r="B23" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137387706</v>
       </c>
       <c r="B24" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
